--- a/salidas/empresas/INTC.xlsx
+++ b/salidas/empresas/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.45258712768555</v>
+        <v>12.45258808135986</v>
       </c>
       <c r="C2" t="n">
         <v>21.26000022888184</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.1231861114502</v>
+        <v>12.12318801879883</v>
       </c>
       <c r="C3" t="n">
         <v>20.60000038146973</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>11.45229339599609</v>
+        <v>11.45229530334473</v>
       </c>
       <c r="C4" t="n">
         <v>19.45999908447266</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>11.75831031799316</v>
+        <v>11.75832176208496</v>
       </c>
       <c r="C5" t="n">
         <v>19.97999954223633</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>10.65925788879395</v>
+        <v>10.65926170349121</v>
       </c>
       <c r="C6" t="n">
         <v>18.02000045776367</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.2389554977417</v>
+        <v>11.23895168304443</v>
       </c>
       <c r="C7" t="n">
         <v>19</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>10.64742374420166</v>
+        <v>10.64742755889893</v>
       </c>
       <c r="C8" t="n">
         <v>18</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>11.64231109619141</v>
+        <v>11.64230823516846</v>
       </c>
       <c r="C9" t="n">
         <v>19.56999969482422</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>12.69529342651367</v>
+        <v>12.69528865814209</v>
       </c>
       <c r="C11" t="n">
         <v>21.34000015258789</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.79284381866455</v>
+        <v>12.79284572601318</v>
       </c>
       <c r="C12" t="n">
         <v>21.39999961853027</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.10537910461426</v>
+        <v>12.10537624359131</v>
       </c>
       <c r="C13" t="n">
         <v>20.25</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.52981567382812</v>
+        <v>12.52981662750244</v>
       </c>
       <c r="C14" t="n">
         <v>20.95999908447266</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.93577003479004</v>
+        <v>11.93576717376709</v>
       </c>
       <c r="C15" t="n">
         <v>19.86000061035156</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.49703693389893</v>
+        <v>11.49704074859619</v>
       </c>
       <c r="C16" t="n">
         <v>19.1299991607666</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>12.92140102386475</v>
+        <v>12.92140293121338</v>
       </c>
       <c r="C17" t="n">
         <v>21.5</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>13.39912033081055</v>
+        <v>13.3991174697876</v>
       </c>
       <c r="C18" t="n">
         <v>22.18000030517578</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>14.34152889251709</v>
+        <v>14.34153079986572</v>
       </c>
       <c r="C19" t="n">
         <v>23.73999977111816</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.2690372467041</v>
+        <v>14.26904296875</v>
       </c>
       <c r="C20" t="n">
         <v>23.6200008392334</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>15.89577674865723</v>
+        <v>15.89577198028564</v>
       </c>
       <c r="C24" t="n">
         <v>26.07999992370605</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>16.2492847442627</v>
+        <v>16.24928855895996</v>
       </c>
       <c r="C25" t="n">
         <v>26.65999984741211</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>12.8604621887207</v>
+        <v>12.86046028137207</v>
       </c>
       <c r="C26" t="n">
         <v>21.10000038146973</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>12.24566173553467</v>
+        <v>12.2456636428833</v>
       </c>
       <c r="C27" t="n">
         <v>19.96999931335449</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>12.98763751983643</v>
+        <v>12.98763561248779</v>
       </c>
       <c r="C28" t="n">
         <v>21.18000030517578</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>13.64989757537842</v>
+        <v>13.64989185333252</v>
       </c>
       <c r="C29" t="n">
         <v>22.26000022888184</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>14.29893684387207</v>
+        <v>14.29893970489502</v>
       </c>
       <c r="C30" t="n">
         <v>23.18000030517578</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>13.25026988983154</v>
+        <v>13.25026607513428</v>
       </c>
       <c r="C31" t="n">
         <v>21.47999954223633</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>14.19596385955811</v>
+        <v>14.19596004486084</v>
       </c>
       <c r="C33" t="n">
         <v>22.8700008392334</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>9.950210571289062</v>
+        <v>9.95020580291748</v>
       </c>
       <c r="C35" t="n">
         <v>16.03000068664551</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>8.640386581420898</v>
+        <v>8.640388488769531</v>
       </c>
       <c r="C36" t="n">
         <v>13.80000019073486</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>9.178848266601562</v>
+        <v>9.178844451904297</v>
       </c>
       <c r="C37" t="n">
         <v>14.65999984741211</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.058880805969238</v>
+        <v>8.058879852294922</v>
       </c>
       <c r="C39" t="n">
         <v>12.73999977111816</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.981878280639648</v>
+        <v>9.981877326965332</v>
       </c>
       <c r="C41" t="n">
         <v>15.77999973297119</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>10.02819633483887</v>
+        <v>10.0281982421875</v>
       </c>
       <c r="C42" t="n">
         <v>15.72000026702881</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.55767154693604</v>
+        <v>10.55767059326172</v>
       </c>
       <c r="C43" t="n">
         <v>16.54999923706055</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.28007221221924</v>
+        <v>12.28006839752197</v>
       </c>
       <c r="C44" t="n">
         <v>19.25</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.05727577209473</v>
+        <v>13.05727005004883</v>
       </c>
       <c r="C45" t="n">
         <v>20.31999969482422</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.57533836364746</v>
+        <v>12.57533550262451</v>
       </c>
       <c r="C46" t="n">
         <v>19.56999969482422</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>12.27974605560303</v>
+        <v>12.27974510192871</v>
       </c>
       <c r="C47" t="n">
         <v>19.11000061035156</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>12.4316577911377</v>
+        <v>12.43165969848633</v>
       </c>
       <c r="C48" t="n">
         <v>19.20000076293945</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.2086353302002</v>
+        <v>13.20863437652588</v>
       </c>
       <c r="C49" t="n">
         <v>20.39999961853027</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>12.5611572265625</v>
+        <v>12.56115436553955</v>
       </c>
       <c r="C50" t="n">
         <v>19.39999961853027</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>13.39913845062256</v>
+        <v>13.39914131164551</v>
       </c>
       <c r="C51" t="n">
         <v>20.53000068664551</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>14.54781723022461</v>
+        <v>14.54782199859619</v>
       </c>
       <c r="C52" t="n">
         <v>22.29000091552734</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>14.90679264068604</v>
+        <v>14.90679359436035</v>
       </c>
       <c r="C53" t="n">
         <v>22.84000015258789</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.07860660552979</v>
+        <v>14.07860851287842</v>
       </c>
       <c r="C54" t="n">
         <v>21.42000007629395</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>12.7837963104248</v>
+        <v>12.78379917144775</v>
       </c>
       <c r="C55" t="n">
         <v>19.45000076293945</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>13.53964996337891</v>
+        <v>13.53965187072754</v>
       </c>
       <c r="C56" t="n">
         <v>20.60000038146973</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>11.7024621963501</v>
+        <v>11.70246315002441</v>
       </c>
       <c r="C57" t="n">
         <v>17.67000007629395</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>12.71574783325195</v>
+        <v>12.71574974060059</v>
       </c>
       <c r="C58" t="n">
         <v>19.20000076293945</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>13.27867984771729</v>
+        <v>13.27868461608887</v>
       </c>
       <c r="C59" t="n">
         <v>20.04999923706055</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>14.12352275848389</v>
+        <v>14.12352180480957</v>
       </c>
       <c r="C60" t="n">
         <v>21.15999984741211</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>14.03675365447998</v>
+        <v>14.03675651550293</v>
       </c>
       <c r="C61" t="n">
         <v>21.03000068664551</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>14.32376575469971</v>
+        <v>14.32376956939697</v>
       </c>
       <c r="C62" t="n">
         <v>21.45999908447266</v>
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.58344650268555</v>
+        <v>13.58344268798828</v>
       </c>
       <c r="C64" t="n">
         <v>20.18000030517578</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.58260345458984</v>
+        <v>15.58259677886963</v>
       </c>
       <c r="C65" t="n">
         <v>23.14999961853027</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>15.27078247070312</v>
+        <v>15.27078914642334</v>
       </c>
       <c r="C66" t="n">
         <v>22.51000022888184</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>15.03334903717041</v>
+        <v>15.03333473205566</v>
       </c>
       <c r="C67" t="n">
         <v>22.15999984741211</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>15.14867305755615</v>
+        <v>15.14867210388184</v>
       </c>
       <c r="C68" t="n">
         <v>22.32999992370605</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.78951740264893</v>
+        <v>13.78951549530029</v>
       </c>
       <c r="C69" t="n">
         <v>20.1299991607666</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.61839962005615</v>
+        <v>14.61839389801025</v>
       </c>
       <c r="C70" t="n">
         <v>21.34000015258789</v>
@@ -1981,7 +1993,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.21551513671875</v>
+        <v>17.21551322937012</v>
       </c>
       <c r="C72" t="n">
         <v>24.90999984741211</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>16.75938415527344</v>
+        <v>16.75938606262207</v>
       </c>
       <c r="C73" t="n">
         <v>24.25</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>18.25908470153809</v>
+        <v>18.25908660888672</v>
       </c>
       <c r="C74" t="n">
         <v>26.42000007629395</v>
@@ -2097,7 +2109,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>19.58926582336426</v>
+        <v>19.58926963806152</v>
       </c>
       <c r="C76" t="n">
         <v>28.1200008392334</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>19.78432655334473</v>
+        <v>19.78432464599609</v>
       </c>
       <c r="C77" t="n">
         <v>28.39999961853027</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>18.13143157958984</v>
+        <v>18.13143348693848</v>
       </c>
       <c r="C78" t="n">
         <v>25.84000015258789</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>18.69979286193848</v>
+        <v>18.69978904724121</v>
       </c>
       <c r="C79" t="n">
         <v>26.64999961853027</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.0331974029541</v>
+        <v>18.03319931030273</v>
       </c>
       <c r="C80" t="n">
         <v>25.70000076293945</v>
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>16.03936767578125</v>
+        <v>16.03937149047852</v>
       </c>
       <c r="C82" t="n">
         <v>22.65999984741211</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>15.31031322479248</v>
+        <v>15.31030941009521</v>
       </c>
       <c r="C83" t="n">
         <v>21.6299991607666</v>
@@ -2358,7 +2370,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>14.74580097198486</v>
+        <v>14.74580001831055</v>
       </c>
       <c r="C85" t="n">
         <v>20.6200008392334</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>15.04615497589111</v>
+        <v>15.04615688323975</v>
       </c>
       <c r="C86" t="n">
         <v>21.04000091552734</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>15.09221458435059</v>
+        <v>15.09221267700195</v>
       </c>
       <c r="C87" t="n">
         <v>20.8799991607666</v>
@@ -2474,7 +2486,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>17.31123352050781</v>
+        <v>17.31123924255371</v>
       </c>
       <c r="C89" t="n">
         <v>23.95000076293945</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>17.7150821685791</v>
+        <v>17.7150764465332</v>
       </c>
       <c r="C90" t="n">
         <v>24.28000068664551</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>17.67860412597656</v>
+        <v>17.67860221862793</v>
       </c>
       <c r="C91" t="n">
         <v>24.22999954223633</v>
@@ -2590,7 +2602,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>16.19388580322266</v>
+        <v>16.19387817382812</v>
       </c>
       <c r="C93" t="n">
         <v>21.97999954223633</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>16.88643646240234</v>
+        <v>16.88642883300781</v>
       </c>
       <c r="C94" t="n">
         <v>22.92000007629395</v>
@@ -2677,7 +2689,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>17.72866821289062</v>
+        <v>17.72867012023926</v>
       </c>
       <c r="C96" t="n">
         <v>23.84000015258789</v>
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>18.24923133850098</v>
+        <v>18.24922943115234</v>
       </c>
       <c r="C98" t="n">
         <v>24.54000091552734</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>18.58841705322266</v>
+        <v>18.58841896057129</v>
       </c>
       <c r="C99" t="n">
         <v>24.76000022888184</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>19.3766975402832</v>
+        <v>19.3766918182373</v>
       </c>
       <c r="C100" t="n">
         <v>25.80999946594238</v>
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>20.68655204772949</v>
+        <v>20.68655967712402</v>
       </c>
       <c r="C102" t="n">
         <v>27.31999969482422</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>23.39731407165527</v>
+        <v>23.39731597900391</v>
       </c>
       <c r="C103" t="n">
         <v>30.89999961853027</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>25.66132736206055</v>
+        <v>25.66133117675781</v>
       </c>
       <c r="C104" t="n">
         <v>33.88999938964844</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>26.61712455749512</v>
+        <v>26.61711311340332</v>
       </c>
       <c r="C105" t="n">
         <v>34.91999816894531</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>26.54089736938477</v>
+        <v>26.54090118408203</v>
       </c>
       <c r="C106" t="n">
         <v>34.81999969482422</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>25.92349243164062</v>
+        <v>25.92348670959473</v>
       </c>
       <c r="C107" t="n">
         <v>34.0099983215332</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>28.57928848266602</v>
+        <v>28.57929420471191</v>
       </c>
       <c r="C108" t="n">
         <v>37.25</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>27.8427562713623</v>
+        <v>27.84275436401367</v>
       </c>
       <c r="C109" t="n">
         <v>36.29000091552734</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>25.34925651550293</v>
+        <v>25.34925842285156</v>
       </c>
       <c r="C110" t="n">
         <v>33.04000091552734</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>25.69335556030273</v>
+        <v>25.6933536529541</v>
       </c>
       <c r="C111" t="n">
         <v>33.25</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>24.16335105895996</v>
+        <v>24.1633472442627</v>
       </c>
       <c r="C112" t="n">
         <v>31.27000045776367</v>
@@ -3199,7 +3211,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>26.82091331481934</v>
+        <v>26.82090377807617</v>
       </c>
       <c r="C114" t="n">
         <v>34.45999908447266</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>23.67649841308594</v>
+        <v>23.67649269104004</v>
       </c>
       <c r="C115" t="n">
         <v>30.42000007629395</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>22.53236770629883</v>
+        <v>22.53237152099609</v>
       </c>
       <c r="C116" t="n">
         <v>28.95000076293945</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>22.39779090881348</v>
+        <v>22.39778709411621</v>
       </c>
       <c r="C117" t="n">
         <v>28.54000091552734</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>23.65344619750977</v>
+        <v>23.6534538269043</v>
       </c>
       <c r="C118" t="n">
         <v>30.13999938964844</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>26.5728588104248</v>
+        <v>26.57285308837891</v>
       </c>
       <c r="C119" t="n">
         <v>33.86000061035156</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>27.47922325134277</v>
+        <v>27.47922897338867</v>
       </c>
       <c r="C120" t="n">
         <v>34.77000045776367</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>27.22631454467773</v>
+        <v>27.2263240814209</v>
       </c>
       <c r="C121" t="n">
         <v>34.45000076293945</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>24.51555061340332</v>
+        <v>24.51554489135742</v>
       </c>
       <c r="C122" t="n">
         <v>31.02000045776367</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>23.59122657775879</v>
+        <v>23.59122848510742</v>
       </c>
       <c r="C123" t="n">
         <v>29.59000015258789</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>25.79169273376465</v>
+        <v>25.79169082641602</v>
       </c>
       <c r="C124" t="n">
         <v>32.34999847412109</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>24.14134407043457</v>
+        <v>24.14134216308594</v>
       </c>
       <c r="C125" t="n">
         <v>30.28000068664551</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>25.40331840515137</v>
+        <v>25.4033203125</v>
       </c>
       <c r="C126" t="n">
         <v>31.59000015258789</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>26.37635231018066</v>
+        <v>26.37635040283203</v>
       </c>
       <c r="C127" t="n">
         <v>32.79999923706055</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>28.03291702270508</v>
+        <v>28.03290367126465</v>
       </c>
       <c r="C128" t="n">
         <v>34.86000061035156</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.07996368408203</v>
+        <v>29.0799617767334</v>
       </c>
       <c r="C129" t="n">
         <v>35.88999938964844</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.5870418548584</v>
+        <v>30.5870361328125</v>
       </c>
       <c r="C130" t="n">
         <v>37.75</v>
@@ -3721,7 +3733,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>29.6103687286377</v>
+        <v>29.61037254333496</v>
       </c>
       <c r="C133" t="n">
         <v>36.27000045776367</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.05937767028809</v>
+        <v>30.05938339233398</v>
       </c>
       <c r="C134" t="n">
         <v>36.81999969482422</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>29.76419448852539</v>
+        <v>29.76420211791992</v>
       </c>
       <c r="C135" t="n">
         <v>36.20000076293945</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>29.65730476379395</v>
+        <v>29.65730667114258</v>
       </c>
       <c r="C136" t="n">
         <v>36.06999969482422</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.72308731079102</v>
+        <v>29.72308540344238</v>
       </c>
       <c r="C137" t="n">
         <v>36.15000152587891</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>29.91107940673828</v>
+        <v>29.91107559204102</v>
       </c>
       <c r="C138" t="n">
         <v>36.11000061035156</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>27.94792556762695</v>
+        <v>27.94793128967285</v>
       </c>
       <c r="C139" t="n">
         <v>33.7400016784668</v>
@@ -3982,7 +3994,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>29.26768493652344</v>
+        <v>29.26767539978027</v>
       </c>
       <c r="C141" t="n">
         <v>35.06999969482422</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>31.77968215942383</v>
+        <v>31.77967643737793</v>
       </c>
       <c r="C142" t="n">
         <v>38.08000183105469</v>
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>37.64299774169922</v>
+        <v>37.64301300048828</v>
       </c>
       <c r="C144" t="n">
         <v>44.84000015258789</v>
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>40.413330078125</v>
+        <v>40.41333770751953</v>
       </c>
       <c r="C146" t="n">
         <v>48.13999938964844</v>
@@ -4185,7 +4197,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>44.01755523681641</v>
+        <v>44.01757049560547</v>
       </c>
       <c r="C148" t="n">
         <v>52.08000183105469</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>43.62876892089844</v>
+        <v>43.6287727355957</v>
       </c>
       <c r="C149" t="n">
         <v>51.61999893188477</v>
@@ -4272,7 +4284,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.25694274902344</v>
+        <v>42.25695037841797</v>
       </c>
       <c r="C151" t="n">
         <v>49.70999908447266</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>40.88833236694336</v>
+        <v>40.88832855224609</v>
       </c>
       <c r="C152" t="n">
         <v>48.09999847412109</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>41.41921997070312</v>
+        <v>41.41922378540039</v>
       </c>
       <c r="C153" t="n">
         <v>48.43000030517578</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>40.44424819946289</v>
+        <v>40.44426345825195</v>
       </c>
       <c r="C154" t="n">
         <v>47.29000091552734</v>
@@ -4417,7 +4429,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>42.43722915649414</v>
+        <v>42.43723297119141</v>
       </c>
       <c r="C156" t="n">
         <v>49.31000137329102</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>40.38895034790039</v>
+        <v>40.38894653320312</v>
       </c>
       <c r="C157" t="n">
         <v>46.93000030517578</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>40.55247116088867</v>
+        <v>40.55246353149414</v>
       </c>
       <c r="C158" t="n">
         <v>47.11999893188477</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>45.86740112304688</v>
+        <v>45.86740493774414</v>
       </c>
       <c r="C159" t="n">
         <v>52.95999908447266</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>46.50829315185547</v>
+        <v>46.50830078125</v>
       </c>
       <c r="C160" t="n">
         <v>53.70000076293945</v>
@@ -4591,7 +4603,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>38.37558746337891</v>
+        <v>38.37559509277344</v>
       </c>
       <c r="C162" t="n">
         <v>44.04000091552734</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>41.71298599243164</v>
+        <v>41.71297454833984</v>
       </c>
       <c r="C163" t="n">
         <v>47.86999893188477</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>44.04827880859375</v>
+        <v>44.04828643798828</v>
       </c>
       <c r="C164" t="n">
         <v>50.54999923706055</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>41.59107208251953</v>
+        <v>41.59106826782227</v>
       </c>
       <c r="C165" t="n">
         <v>47.40999984741211</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>45.20539855957031</v>
+        <v>45.20540618896484</v>
       </c>
       <c r="C166" t="n">
         <v>51.52999877929688</v>
@@ -4765,7 +4777,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>51.2054328918457</v>
+        <v>51.20542526245117</v>
       </c>
       <c r="C168" t="n">
         <v>58.04999923706055</v>
@@ -4823,7 +4835,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4852,7 +4864,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4881,7 +4893,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>47.97391891479492</v>
+        <v>47.97389602661133</v>
       </c>
       <c r="C172" t="n">
         <v>54.11999893188477</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>53.16841506958008</v>
+        <v>53.16842269897461</v>
       </c>
       <c r="C173" t="n">
         <v>59.97999954223633</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>56.09850692749023</v>
+        <v>56.0985221862793</v>
       </c>
       <c r="C174" t="n">
         <v>62.93000030517578</v>
@@ -4997,11 +5009,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>53.33504104614258</v>
+        <v>53.33504486083984</v>
       </c>
       <c r="C175" t="n">
         <v>59.83000183105469</v>
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>42.54858016967773</v>
+        <v>42.548583984375</v>
       </c>
       <c r="C176" t="n">
         <v>47.72999954223633</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>45.72749710083008</v>
+        <v>45.72749328613281</v>
       </c>
       <c r="C177" t="n">
         <v>50.95000076293945</v>
@@ -5084,7 +5096,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>39.74118041992188</v>
+        <v>39.74118423461914</v>
       </c>
       <c r="C179" t="n">
         <v>44.27999877929688</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>43.70962142944336</v>
+        <v>43.70962524414062</v>
       </c>
       <c r="C180" t="n">
         <v>48.34999847412109</v>
@@ -5171,7 +5183,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>50.18243789672852</v>
+        <v>50.18244552612305</v>
       </c>
       <c r="C182" t="n">
         <v>55.5099983215332</v>
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>55.28017425537109</v>
+        <v>55.28018188476562</v>
       </c>
       <c r="C183" t="n">
         <v>60.77999877929688</v>
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>58.20880889892578</v>
+        <v>58.20881652832031</v>
       </c>
       <c r="C184" t="n">
         <v>64</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>52.32425689697266</v>
+        <v>52.32426452636719</v>
       </c>
       <c r="C185" t="n">
         <v>57.52999877929688</v>
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>52.27132797241211</v>
+        <v>52.27134323120117</v>
       </c>
       <c r="C186" t="n">
         <v>57.11999893188477</v>
@@ -5345,7 +5357,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>49.15995025634766</v>
+        <v>49.15994644165039</v>
       </c>
       <c r="C188" t="n">
         <v>53.72000122070312</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>49.79256820678711</v>
+        <v>49.79256439208984</v>
       </c>
       <c r="C189" t="n">
         <v>54.06000137329102</v>
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>49.07413864135742</v>
+        <v>49.07414245605469</v>
       </c>
       <c r="C190" t="n">
         <v>53.27999877929688</v>
@@ -5461,11 +5473,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>45.13199615478516</v>
+        <v>45.13200759887695</v>
       </c>
       <c r="C191" t="n">
         <v>49</v>
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5519,11 +5531,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>47.7645149230957</v>
+        <v>47.76451873779297</v>
       </c>
       <c r="C193" t="n">
         <v>51.5</v>
@@ -5548,7 +5560,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>44.5771598815918</v>
+        <v>44.57715606689453</v>
       </c>
       <c r="C195" t="n">
         <v>47.70000076293945</v>
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>46.31538772583008</v>
+        <v>46.31538009643555</v>
       </c>
       <c r="C196" t="n">
         <v>49.56000137329102</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>40.73622512817383</v>
+        <v>40.73622894287109</v>
       </c>
       <c r="C197" t="n">
         <v>43.59000015258789</v>
@@ -5664,11 +5676,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>41.84003448486328</v>
+        <v>41.84003067016602</v>
       </c>
       <c r="C198" t="n">
         <v>44.41999816894531</v>
@@ -5693,7 +5705,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5722,11 +5734,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>34.20107269287109</v>
+        <v>34.20106887817383</v>
       </c>
       <c r="C200" t="n">
         <v>36.31000137329102</v>
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>30.36957359313965</v>
+        <v>30.36957550048828</v>
       </c>
       <c r="C201" t="n">
         <v>31.92000007629395</v>
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>24.51829528808594</v>
+        <v>24.51829147338867</v>
       </c>
       <c r="C202" t="n">
         <v>25.77000045776367</v>
@@ -5809,11 +5821,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>27.0490894317627</v>
+        <v>27.04909133911133</v>
       </c>
       <c r="C203" t="n">
         <v>28.43000030517578</v>
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>28.99583053588867</v>
+        <v>28.9958324432373</v>
       </c>
       <c r="C204" t="n">
         <v>30.06999969482422</v>
@@ -5867,7 +5879,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5896,7 +5908,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>24.33236503601074</v>
+        <v>24.33236312866211</v>
       </c>
       <c r="C207" t="n">
         <v>24.93000030517578</v>
@@ -5954,11 +5966,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>31.88681602478027</v>
+        <v>31.88681221008301</v>
       </c>
       <c r="C208" t="n">
         <v>32.66999816894531</v>
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>30.31541061401367</v>
+        <v>30.31540870666504</v>
       </c>
       <c r="C209" t="n">
         <v>31.05999946594238</v>
@@ -6010,11 +6022,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>30.81196403503418</v>
+        <v>30.81196594238281</v>
       </c>
       <c r="C210" t="n">
         <v>31.44000053405762</v>
@@ -6037,7 +6049,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6064,11 +6076,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>35.05546951293945</v>
+        <v>35.05547332763672</v>
       </c>
       <c r="C212" t="n">
         <v>35.77000045776367</v>
@@ -6091,11 +6103,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>34.56194686889648</v>
+        <v>34.56195068359375</v>
       </c>
       <c r="C213" t="n">
         <v>35.13999938964844</v>
@@ -6118,11 +6130,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>34.96520614624023</v>
+        <v>34.96520233154297</v>
       </c>
       <c r="C214" t="n">
         <v>35.54999923706055</v>
@@ -6145,7 +6157,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6172,11 +6184,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>44.1092529296875</v>
+        <v>44.10924911499023</v>
       </c>
       <c r="C216" t="n">
         <v>44.70000076293945</v>
@@ -6199,7 +6211,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6226,7 +6238,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6255,7 +6267,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6284,7 +6296,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6313,7 +6325,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6342,7 +6354,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6371,7 +6383,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6400,7 +6412,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6429,7 +6441,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6458,7 +6470,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6487,7 +6499,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6516,7 +6528,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6543,7 +6555,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6570,7 +6582,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6597,7 +6609,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6624,7 +6636,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6651,7 +6663,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6678,7 +6690,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6705,7 +6717,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6732,7 +6744,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6759,7 +6771,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6786,7 +6798,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6813,7 +6825,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6840,7 +6852,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6869,7 +6881,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6925,7 +6937,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6952,7 +6964,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6979,7 +6991,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7006,7 +7018,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7060,7 +7072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7087,7 +7099,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7114,17 +7126,17 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>122.5999984741211</v>
+        <v>127.3899993896484</v>
       </c>
       <c r="C250" t="n">
-        <v>122.5999984741211</v>
+        <v>127.3899993896484</v>
       </c>
       <c r="D250" t="n">
-        <v>1745408900</v>
+        <v>1864830100</v>
       </c>
       <c r="E250" t="n">
         <v>-2.09</v>
@@ -7134,10 +7146,10 @@
         <v>5044000000</v>
       </c>
       <c r="H250" t="n">
-        <v>618394392303.4668</v>
+        <v>642555156921.3867</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3460366574147502</v>
+        <v>0.3697125495638382</v>
       </c>
     </row>
   </sheetData>
@@ -7169,75 +7181,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39536</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39627</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40028</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7273,13 +7285,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39628</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39718</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39810</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39900</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39900</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39991</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40028</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40082</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40174</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40264</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40265</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40355</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7525,13 +7537,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40356</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40446</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7567,13 +7579,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40447</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40537</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7600,7 +7612,7 @@
       <c r="I10" t="n">
         <v>2.01</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K10" t="n">
@@ -7613,13 +7625,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40538</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40635</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7646,7 +7658,7 @@
       <c r="I11" t="n">
         <v>2.14</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K11" t="n">
@@ -7659,13 +7671,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40636</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7692,7 +7704,7 @@
       <c r="I12" t="n">
         <v>2.17</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K12" t="n">
@@ -7705,13 +7717,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40727</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7738,7 +7750,7 @@
       <c r="I13" t="n">
         <v>2.3</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K13" t="n">
@@ -7751,13 +7763,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40818</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7784,7 +7796,7 @@
       <c r="I14" t="n">
         <v>2.390000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K14" t="n">
@@ -7797,13 +7809,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7830,7 +7842,7 @@
       <c r="I15" t="n">
         <v>2.36</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K15" t="n">
@@ -7843,13 +7855,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7876,7 +7888,7 @@
       <c r="I16" t="n">
         <v>2.36</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K16" t="n">
@@ -7889,13 +7901,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7922,7 +7934,7 @@
       <c r="I17" t="n">
         <v>2.29</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="K17" t="n">
@@ -7935,13 +7947,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41272</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7968,7 +7980,7 @@
       <c r="I18" t="n">
         <v>2.13</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="K18" t="n">
@@ -7981,13 +7993,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41393</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8014,7 +8026,7 @@
       <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41393</v>
       </c>
       <c r="K19" t="n">
@@ -8027,13 +8039,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41484</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8060,7 +8072,7 @@
       <c r="I20" t="n">
         <v>1.85</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41484</v>
       </c>
       <c r="K20" t="n">
@@ -8073,13 +8085,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41575</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8106,7 +8118,7 @@
       <c r="I21" t="n">
         <v>1.85</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41575</v>
       </c>
       <c r="K21" t="n">
@@ -8119,13 +8131,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41636</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8152,7 +8164,7 @@
       <c r="I22" t="n">
         <v>1.89</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K22" t="n">
@@ -8165,13 +8177,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8198,7 +8210,7 @@
       <c r="I23" t="n">
         <v>1.87</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K23" t="n">
@@ -8211,13 +8223,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8244,7 +8256,7 @@
       <c r="I24" t="n">
         <v>2.03</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K24" t="n">
@@ -8257,13 +8269,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8290,7 +8302,7 @@
       <c r="I25" t="n">
         <v>2.11</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K25" t="n">
@@ -8303,13 +8315,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42000</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8336,7 +8348,7 @@
       <c r="I26" t="n">
         <v>2.31</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K26" t="n">
@@ -8349,13 +8361,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42091</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8382,7 +8394,7 @@
       <c r="I27" t="n">
         <v>2.34</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="K27" t="n">
@@ -8395,13 +8407,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42182</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42212</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8428,7 +8440,7 @@
       <c r="I28" t="n">
         <v>2.34</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42212</v>
       </c>
       <c r="K28" t="n">
@@ -8441,13 +8453,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42273</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8474,7 +8486,7 @@
       <c r="I29" t="n">
         <v>2.32</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="K29" t="n">
@@ -8487,13 +8499,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42364</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8520,7 +8532,7 @@
       <c r="I30" t="n">
         <v>2.33</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="K30" t="n">
@@ -8533,13 +8545,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42365</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42462</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8566,7 +8578,7 @@
       <c r="I31" t="n">
         <v>2.34</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="K31" t="n">
@@ -8579,13 +8591,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42553</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8612,7 +8624,7 @@
       <c r="I32" t="n">
         <v>2.06</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="K32" t="n">
@@ -8625,13 +8637,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42554</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8658,7 +8670,7 @@
       <c r="I33" t="n">
         <v>2.11</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="K33" t="n">
@@ -8671,13 +8683,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8704,7 +8716,7 @@
       <c r="I34" t="n">
         <v>2.12</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K34" t="n">
@@ -8717,13 +8729,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8750,7 +8762,7 @@
       <c r="I35" t="n">
         <v>2.31</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K35" t="n">
@@ -8763,13 +8775,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8796,7 +8808,7 @@
       <c r="I36" t="n">
         <v>2.62</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K36" t="n">
@@ -8809,13 +8821,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8842,7 +8854,7 @@
       <c r="I37" t="n">
         <v>2.87</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K37" t="n">
@@ -8855,13 +8867,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43099</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8888,7 +8900,7 @@
       <c r="I38" t="n">
         <v>1.99</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K38" t="n">
@@ -8901,13 +8913,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8934,7 +8946,7 @@
       <c r="I39" t="n">
         <v>2.31</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K39" t="n">
@@ -8947,13 +8959,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8980,7 +8992,7 @@
       <c r="I40" t="n">
         <v>2.78</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K40" t="n">
@@ -8993,13 +9005,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9026,7 +9038,7 @@
       <c r="I41" t="n">
         <v>3.22</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K41" t="n">
@@ -9039,13 +9051,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43463</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9072,7 +9084,7 @@
       <c r="I42" t="n">
         <v>4.48</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="K42" t="n">
@@ -9085,13 +9097,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9118,7 +9130,7 @@
       <c r="I43" t="n">
         <v>4.420000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K43" t="n">
@@ -9131,13 +9143,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9164,7 +9176,7 @@
       <c r="I44" t="n">
         <v>4.29</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K44" t="n">
@@ -9177,13 +9189,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9210,7 +9222,7 @@
       <c r="I45" t="n">
         <v>4.260000000000001</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K45" t="n">
@@ -9223,13 +9235,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43827</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9256,7 +9268,7 @@
       <c r="I46" t="n">
         <v>4.71</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="K46" t="n">
@@ -9269,13 +9281,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43918</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9302,7 +9314,7 @@
       <c r="I47" t="n">
         <v>5.149999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="K47" t="n">
@@ -9315,13 +9327,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44009</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9348,7 +9360,7 @@
       <c r="I48" t="n">
         <v>5.42</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="K48" t="n">
@@ -9361,13 +9373,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44100</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9394,7 +9406,7 @@
       <c r="I49" t="n">
         <v>5.09</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="K49" t="n">
@@ -9407,13 +9419,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44191</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9440,7 +9452,7 @@
       <c r="I50" t="n">
         <v>4.94</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="K50" t="n">
@@ -9453,13 +9465,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44282</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9486,7 +9498,7 @@
       <c r="I51" t="n">
         <v>4.45</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="K51" t="n">
@@ -9499,13 +9511,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44373</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9532,7 +9544,7 @@
       <c r="I52" t="n">
         <v>4.5</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="K52" t="n">
@@ -9545,13 +9557,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44374</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44464</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9578,7 +9590,7 @@
       <c r="I53" t="n">
         <v>5.15</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="K53" t="n">
@@ -9591,13 +9603,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44465</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44555</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9624,7 +9636,7 @@
       <c r="I54" t="n">
         <v>4.859999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="K54" t="n">
@@ -9637,13 +9649,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44556</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44653</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9670,7 +9682,7 @@
       <c r="I55" t="n">
         <v>6.02</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K55" t="n">
@@ -9683,13 +9695,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44654</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44744</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9716,7 +9728,7 @@
       <c r="I56" t="n">
         <v>4.669999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K56" t="n">
@@ -9729,13 +9741,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44745</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9762,7 +9774,7 @@
       <c r="I57" t="n">
         <v>3.25</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K57" t="n">
@@ -9775,13 +9787,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44836</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9808,7 +9820,7 @@
       <c r="I58" t="n">
         <v>1.94</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="K58" t="n">
@@ -9821,13 +9833,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9854,7 +9866,7 @@
       <c r="I59" t="n">
         <v>-0.7000000000000006</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K59" t="n">
@@ -9867,13 +9879,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9900,7 +9912,7 @@
       <c r="I60" t="n">
         <v>-0.2400000000000007</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="K60" t="n">
@@ -9913,13 +9925,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9946,7 +9958,7 @@
       <c r="I61" t="n">
         <v>-0.4200000000000007</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K61" t="n">
@@ -9959,13 +9971,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9992,7 +10004,7 @@
       <c r="I62" t="n">
         <v>0.3999999999999996</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="K62" t="n">
@@ -10005,13 +10017,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10038,7 +10050,7 @@
       <c r="I63" t="n">
         <v>0.9699999999999996</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K63" t="n">
@@ -10051,13 +10063,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10084,7 +10096,7 @@
       <c r="I64" t="n">
         <v>0.2399999999999998</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K64" t="n">
@@ -10097,13 +10109,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10130,7 +10142,7 @@
       <c r="I65" t="n">
         <v>-3.71</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K65" t="n">
@@ -10143,13 +10155,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10176,7 +10188,7 @@
       <c r="I66" t="n">
         <v>-4.38</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K66" t="n">
@@ -10189,13 +10201,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10222,7 +10234,7 @@
       <c r="I67" t="n">
         <v>-4.48</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K67" t="n">
@@ -10235,13 +10247,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10268,7 +10280,7 @@
       <c r="I68" t="n">
         <v>-4.77</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K68" t="n">
@@ -10281,13 +10293,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10314,7 +10326,7 @@
       <c r="I69" t="n">
         <v>0.009999999999999676</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K69" t="n">
@@ -10327,13 +10339,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46018</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10360,7 +10372,7 @@
       <c r="I70" t="n">
         <v>-0.06</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="K70" t="n">
@@ -10373,13 +10385,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10406,7 +10418,7 @@
       <c r="I71" t="n">
         <v>-0.6</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="K71" t="n">
@@ -10419,13 +10431,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46200</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10452,7 +10464,7 @@
       <c r="I72" t="n">
         <v>-2.09</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="K72" t="n">
@@ -10489,52 +10501,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40018</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40028</v>
       </c>
       <c r="C2" t="n">
@@ -10563,10 +10575,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40109</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="C3" t="n">
@@ -10595,10 +10607,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40214</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40231</v>
       </c>
       <c r="C4" t="n">
@@ -10627,10 +10639,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40291</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="C5" t="n">
@@ -10659,10 +10671,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40382</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="C6" t="n">
@@ -10691,10 +10703,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40473</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="C7" t="n">
@@ -10723,10 +10735,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40578</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C8" t="n">
@@ -10755,10 +10767,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10787,10 +10799,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C10" t="n">
@@ -10819,10 +10831,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10851,10 +10863,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40949</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C12" t="n">
@@ -10883,10 +10895,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C13" t="n">
@@ -10915,10 +10927,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41117</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C14" t="n">
@@ -10947,10 +10959,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41201</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C15" t="n">
@@ -10979,10 +10991,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41313</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="C16" t="n">
@@ -11011,10 +11023,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41383</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41393</v>
       </c>
       <c r="C17" t="n">
@@ -11043,10 +11055,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41474</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41484</v>
       </c>
       <c r="C18" t="n">
@@ -11075,10 +11087,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41575</v>
       </c>
       <c r="C19" t="n">
@@ -11107,10 +11119,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41677</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C20" t="n">
@@ -11139,10 +11151,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41747</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C21" t="n">
@@ -11171,10 +11183,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="C22" t="n">
@@ -11203,10 +11215,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41929</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C23" t="n">
@@ -11235,10 +11247,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42041</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C24" t="n">
@@ -11267,10 +11279,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="C25" t="n">
@@ -11299,10 +11311,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42202</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42212</v>
       </c>
       <c r="C26" t="n">
@@ -11331,10 +11343,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42293</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C27" t="n">
@@ -11363,10 +11375,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42405</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="C28" t="n">
@@ -11395,10 +11407,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="C29" t="n">
@@ -11427,10 +11439,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C30" t="n">
@@ -11459,10 +11471,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="C31" t="n">
@@ -11491,10 +11503,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42773</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C32" t="n">
@@ -11523,10 +11535,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11555,10 +11567,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C34" t="n">
@@ -11587,10 +11599,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C35" t="n">
@@ -11619,10 +11631,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43138</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C36" t="n">
@@ -11651,10 +11663,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11683,10 +11695,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11715,10 +11727,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11747,10 +11759,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43491</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="C40" t="n">
@@ -11779,10 +11791,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11811,10 +11823,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11843,10 +11855,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C43" t="n">
@@ -11875,10 +11887,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43847</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="C44" t="n">
@@ -11907,10 +11919,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43918</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="C45" t="n">
@@ -11939,10 +11951,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44009</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="C46" t="n">
@@ -11971,10 +11983,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44100</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="C47" t="n">
@@ -12003,10 +12015,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44211</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="C48" t="n">
@@ -12035,10 +12047,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44282</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="C49" t="n">
@@ -12067,10 +12079,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44373</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="C50" t="n">
@@ -12099,10 +12111,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44464</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="C51" t="n">
@@ -12131,10 +12143,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44582</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="C52" t="n">
@@ -12163,10 +12175,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44653</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12195,10 +12207,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44744</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C54" t="n">
@@ -12227,10 +12239,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12259,10 +12271,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44946</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="C56" t="n">
@@ -12291,10 +12303,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C57" t="n">
@@ -12323,10 +12335,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="C58" t="n">
@@ -12355,10 +12367,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C59" t="n">
@@ -12387,10 +12399,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45310</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="C60" t="n">
@@ -12419,10 +12431,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C61" t="n">
@@ -12451,10 +12463,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C62" t="n">
@@ -12483,10 +12495,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C63" t="n">
@@ -12515,10 +12527,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45681</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C64" t="n">
@@ -12547,10 +12559,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45765</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C65" t="n">
@@ -12579,10 +12591,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C66" t="n">
@@ -12611,10 +12623,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C67" t="n">
@@ -12643,10 +12655,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46038</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="C68" t="n">
@@ -12675,10 +12687,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="C69" t="n">
@@ -12707,10 +12719,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="C70" t="n">
@@ -12757,12 +12769,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/INTC.xlsx
+++ b/salidas/empresas/INTC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.45258808135986</v>
+        <v>12.45258140563965</v>
       </c>
       <c r="C2" t="n">
         <v>21.26000022888184</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.12318801879883</v>
+        <v>12.12318992614746</v>
       </c>
       <c r="C3" t="n">
         <v>20.60000038146973</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>11.45229530334473</v>
+        <v>11.45228576660156</v>
       </c>
       <c r="C4" t="n">
         <v>19.45999908447266</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>11.75832176208496</v>
+        <v>11.75831890106201</v>
       </c>
       <c r="C5" t="n">
         <v>19.97999954223633</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>10.65926170349121</v>
+        <v>10.659255027771</v>
       </c>
       <c r="C6" t="n">
         <v>18.02000045776367</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.23895168304443</v>
+        <v>11.23894691467285</v>
       </c>
       <c r="C7" t="n">
         <v>19</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>10.64742755889893</v>
+        <v>10.64742469787598</v>
       </c>
       <c r="C8" t="n">
         <v>18</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>11.64230823516846</v>
+        <v>11.64230632781982</v>
       </c>
       <c r="C9" t="n">
         <v>19.56999969482422</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.23721122741699</v>
+        <v>12.23721313476562</v>
       </c>
       <c r="C10" t="n">
         <v>20.56999969482422</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>12.69528865814209</v>
+        <v>12.69528675079346</v>
       </c>
       <c r="C11" t="n">
         <v>21.34000015258789</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.79284572601318</v>
+        <v>12.79284477233887</v>
       </c>
       <c r="C12" t="n">
         <v>21.39999961853027</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.10537624359131</v>
+        <v>12.10537433624268</v>
       </c>
       <c r="C13" t="n">
         <v>20.25</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.52981662750244</v>
+        <v>12.52981376647949</v>
       </c>
       <c r="C14" t="n">
         <v>20.95999908447266</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.93576717376709</v>
+        <v>11.93577289581299</v>
       </c>
       <c r="C15" t="n">
         <v>19.86000061035156</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.49704074859619</v>
+        <v>11.49704170227051</v>
       </c>
       <c r="C16" t="n">
         <v>19.1299991607666</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>12.92140293121338</v>
+        <v>12.92139530181885</v>
       </c>
       <c r="C17" t="n">
         <v>21.5</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>13.3991174697876</v>
+        <v>13.39911651611328</v>
       </c>
       <c r="C18" t="n">
         <v>22.18000030517578</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>14.34153079986572</v>
+        <v>14.34152793884277</v>
       </c>
       <c r="C19" t="n">
         <v>23.73999977111816</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.26904296875</v>
+        <v>14.26903247833252</v>
       </c>
       <c r="C20" t="n">
         <v>23.6200008392334</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.62845802307129</v>
+        <v>15.62846565246582</v>
       </c>
       <c r="C21" t="n">
         <v>25.75</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.69522285461426</v>
+        <v>15.69522762298584</v>
       </c>
       <c r="C22" t="n">
         <v>25.86000061035156</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>16.3264331817627</v>
+        <v>16.32643508911133</v>
       </c>
       <c r="C23" t="n">
         <v>26.89999961853027</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>12.86046028137207</v>
+        <v>12.86046123504639</v>
       </c>
       <c r="C26" t="n">
         <v>21.10000038146973</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>12.2456636428833</v>
+        <v>12.24565982818604</v>
       </c>
       <c r="C27" t="n">
         <v>19.96999931335449</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>12.98763561248779</v>
+        <v>12.98763847351074</v>
       </c>
       <c r="C28" t="n">
         <v>21.18000030517578</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>13.64989185333252</v>
+        <v>13.64989757537842</v>
       </c>
       <c r="C29" t="n">
         <v>22.26000022888184</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>14.29893970489502</v>
+        <v>14.29893398284912</v>
       </c>
       <c r="C30" t="n">
         <v>23.18000030517578</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>13.68823719024658</v>
+        <v>13.6882438659668</v>
       </c>
       <c r="C32" t="n">
         <v>22.19000053405762</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>14.19596004486084</v>
+        <v>14.19596481323242</v>
       </c>
       <c r="C33" t="n">
         <v>22.8700008392334</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>11.62616443634033</v>
+        <v>11.62616348266602</v>
       </c>
       <c r="C34" t="n">
         <v>18.72999954223633</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>9.95020580291748</v>
+        <v>9.950210571289062</v>
       </c>
       <c r="C35" t="n">
         <v>16.03000068664551</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>8.640388488769531</v>
+        <v>8.640389442443848</v>
       </c>
       <c r="C36" t="n">
         <v>13.80000019073486</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>9.178844451904297</v>
+        <v>9.178847312927246</v>
       </c>
       <c r="C37" t="n">
         <v>14.65999984741211</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.076884269714355</v>
+        <v>8.076885223388672</v>
       </c>
       <c r="C38" t="n">
         <v>12.89999961853027</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.058879852294922</v>
+        <v>8.058877944946289</v>
       </c>
       <c r="C39" t="n">
         <v>12.73999977111816</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.981877326965332</v>
+        <v>9.981880187988281</v>
       </c>
       <c r="C41" t="n">
         <v>15.77999973297119</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>10.0281982421875</v>
+        <v>10.02819061279297</v>
       </c>
       <c r="C42" t="n">
         <v>15.72000026702881</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.55767059326172</v>
+        <v>10.55767345428467</v>
       </c>
       <c r="C43" t="n">
         <v>16.54999923706055</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.28006839752197</v>
+        <v>12.28007411956787</v>
       </c>
       <c r="C44" t="n">
         <v>19.25</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.05727005004883</v>
+        <v>13.05726718902588</v>
       </c>
       <c r="C45" t="n">
         <v>20.31999969482422</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.57533550262451</v>
+        <v>12.57533645629883</v>
       </c>
       <c r="C46" t="n">
         <v>19.56999969482422</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>12.27974510192871</v>
+        <v>12.27974987030029</v>
       </c>
       <c r="C47" t="n">
         <v>19.11000061035156</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>12.43165969848633</v>
+        <v>12.43165493011475</v>
       </c>
       <c r="C48" t="n">
         <v>19.20000076293945</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.20863437652588</v>
+        <v>13.20863246917725</v>
       </c>
       <c r="C49" t="n">
         <v>20.39999961853027</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>12.56115436553955</v>
+        <v>12.56114864349365</v>
       </c>
       <c r="C50" t="n">
         <v>19.39999961853027</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>13.39914131164551</v>
+        <v>13.39914226531982</v>
       </c>
       <c r="C51" t="n">
         <v>20.53000068664551</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>14.54782199859619</v>
+        <v>14.54782295227051</v>
       </c>
       <c r="C52" t="n">
         <v>22.29000091552734</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>14.90679359436035</v>
+        <v>14.90678596496582</v>
       </c>
       <c r="C53" t="n">
         <v>22.84000015258789</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.07860851287842</v>
+        <v>14.0786075592041</v>
       </c>
       <c r="C54" t="n">
         <v>21.42000007629395</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>13.53965187072754</v>
+        <v>13.53965282440186</v>
       </c>
       <c r="C56" t="n">
         <v>20.60000038146973</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>13.27868461608887</v>
+        <v>13.27868843078613</v>
       </c>
       <c r="C59" t="n">
         <v>20.04999923706055</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>14.12352180480957</v>
+        <v>14.12352466583252</v>
       </c>
       <c r="C60" t="n">
         <v>21.15999984741211</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>14.03675651550293</v>
+        <v>14.03675556182861</v>
       </c>
       <c r="C61" t="n">
         <v>21.03000068664551</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>14.32376956939697</v>
+        <v>14.32376480102539</v>
       </c>
       <c r="C62" t="n">
         <v>21.45999908447266</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>14.45176219940186</v>
+        <v>14.45176124572754</v>
       </c>
       <c r="C63" t="n">
         <v>21.46999931335449</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.58344268798828</v>
+        <v>13.58344554901123</v>
       </c>
       <c r="C64" t="n">
         <v>20.18000030517578</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.58259677886963</v>
+        <v>15.58259773254395</v>
       </c>
       <c r="C65" t="n">
         <v>23.14999961853027</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>15.27078914642334</v>
+        <v>15.27078628540039</v>
       </c>
       <c r="C66" t="n">
         <v>22.51000022888184</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>15.03333473205566</v>
+        <v>15.03334999084473</v>
       </c>
       <c r="C67" t="n">
         <v>22.15999984741211</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>15.14867210388184</v>
+        <v>15.14867115020752</v>
       </c>
       <c r="C68" t="n">
         <v>22.32999992370605</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.78951549530029</v>
+        <v>13.78951644897461</v>
       </c>
       <c r="C69" t="n">
         <v>20.1299991607666</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.61839389801025</v>
+        <v>14.6183967590332</v>
       </c>
       <c r="C70" t="n">
         <v>21.34000015258789</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>16.81046867370605</v>
+        <v>16.81047248840332</v>
       </c>
       <c r="C71" t="n">
         <v>24.54000091552734</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.21551322937012</v>
+        <v>17.21551132202148</v>
       </c>
       <c r="C72" t="n">
         <v>24.90999984741211</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>16.75938606262207</v>
+        <v>16.75937843322754</v>
       </c>
       <c r="C73" t="n">
         <v>24.25</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>18.25908660888672</v>
+        <v>18.25908279418945</v>
       </c>
       <c r="C74" t="n">
         <v>26.42000007629395</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>18.72544288635254</v>
+        <v>18.7254467010498</v>
       </c>
       <c r="C75" t="n">
         <v>26.8799991607666</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>19.58926963806152</v>
+        <v>19.58926391601562</v>
       </c>
       <c r="C76" t="n">
         <v>28.1200008392334</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>19.78432464599609</v>
+        <v>19.78431510925293</v>
       </c>
       <c r="C77" t="n">
         <v>28.39999961853027</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>18.13143348693848</v>
+        <v>18.13143539428711</v>
       </c>
       <c r="C78" t="n">
         <v>25.84000015258789</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>18.69978904724121</v>
+        <v>18.69979286193848</v>
       </c>
       <c r="C79" t="n">
         <v>26.64999961853027</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.03319931030273</v>
+        <v>18.03320121765137</v>
       </c>
       <c r="C80" t="n">
         <v>25.70000076293945</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>17.57535743713379</v>
+        <v>17.57535362243652</v>
       </c>
       <c r="C81" t="n">
         <v>24.82999992370605</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>16.03937149047852</v>
+        <v>16.03937721252441</v>
       </c>
       <c r="C82" t="n">
         <v>22.65999984741211</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>15.31030941009521</v>
+        <v>15.31030750274658</v>
       </c>
       <c r="C83" t="n">
         <v>21.6299991607666</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>13.99492740631104</v>
+        <v>13.99492645263672</v>
       </c>
       <c r="C84" t="n">
         <v>19.56999969482422</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>14.74580001831055</v>
+        <v>14.74580383300781</v>
       </c>
       <c r="C85" t="n">
         <v>20.6200008392334</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>15.04615688323975</v>
+        <v>15.04616069793701</v>
       </c>
       <c r="C86" t="n">
         <v>21.04000091552734</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>15.09221267700195</v>
+        <v>15.09221076965332</v>
       </c>
       <c r="C87" t="n">
         <v>20.8799991607666</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>15.78611183166504</v>
+        <v>15.78611469268799</v>
       </c>
       <c r="C88" t="n">
         <v>21.84000015258789</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>17.31123924255371</v>
+        <v>17.31123161315918</v>
       </c>
       <c r="C89" t="n">
         <v>23.95000076293945</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>17.7150764465332</v>
+        <v>17.7150821685791</v>
       </c>
       <c r="C90" t="n">
         <v>24.28000068664551</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>17.67860221862793</v>
+        <v>17.67859649658203</v>
       </c>
       <c r="C91" t="n">
         <v>24.22999954223633</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>17.02924156188965</v>
+        <v>17.02924537658691</v>
       </c>
       <c r="C92" t="n">
         <v>23.34000015258789</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>16.19387817382812</v>
+        <v>16.19388580322266</v>
       </c>
       <c r="C93" t="n">
         <v>21.97999954223633</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>16.88642883300781</v>
+        <v>16.88643264770508</v>
       </c>
       <c r="C94" t="n">
         <v>22.92000007629395</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>18.02840805053711</v>
+        <v>18.02840042114258</v>
       </c>
       <c r="C95" t="n">
         <v>24.46999931335449</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>17.72867012023926</v>
+        <v>17.72866630554199</v>
       </c>
       <c r="C96" t="n">
         <v>23.84000015258789</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>19.30521392822266</v>
+        <v>19.30521202087402</v>
       </c>
       <c r="C97" t="n">
         <v>25.95999908447266</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>18.24922943115234</v>
+        <v>18.24922752380371</v>
       </c>
       <c r="C98" t="n">
         <v>24.54000091552734</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>18.58841896057129</v>
+        <v>18.58841705322266</v>
       </c>
       <c r="C99" t="n">
         <v>24.76000022888184</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>19.3766918182373</v>
+        <v>19.37669372558594</v>
       </c>
       <c r="C100" t="n">
         <v>25.80999946594238</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>20.03734970092773</v>
+        <v>20.03735160827637</v>
       </c>
       <c r="C101" t="n">
         <v>26.69000053405762</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>20.68655967712402</v>
+        <v>20.68655776977539</v>
       </c>
       <c r="C102" t="n">
         <v>27.31999969482422</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>25.66133117675781</v>
+        <v>25.66132164001465</v>
       </c>
       <c r="C104" t="n">
         <v>33.88999938964844</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>26.61711311340332</v>
+        <v>26.61712265014648</v>
       </c>
       <c r="C105" t="n">
         <v>34.91999816894531</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>25.92348670959473</v>
+        <v>25.92349052429199</v>
       </c>
       <c r="C107" t="n">
         <v>34.0099983215332</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>28.57929420471191</v>
+        <v>28.57929801940918</v>
       </c>
       <c r="C108" t="n">
         <v>37.25</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>27.84275436401367</v>
+        <v>27.84275245666504</v>
       </c>
       <c r="C109" t="n">
         <v>36.29000091552734</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>25.6933536529541</v>
+        <v>25.693359375</v>
       </c>
       <c r="C111" t="n">
         <v>33.25</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>24.1633472442627</v>
+        <v>24.16335105895996</v>
       </c>
       <c r="C112" t="n">
         <v>31.27000045776367</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>26.82090377807617</v>
+        <v>26.82090759277344</v>
       </c>
       <c r="C114" t="n">
         <v>34.45999908447266</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>23.67649269104004</v>
+        <v>23.6765022277832</v>
       </c>
       <c r="C115" t="n">
         <v>30.42000007629395</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>22.53237152099609</v>
+        <v>22.53237342834473</v>
       </c>
       <c r="C116" t="n">
         <v>28.95000076293945</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>22.39778709411621</v>
+        <v>22.39779090881348</v>
       </c>
       <c r="C117" t="n">
         <v>28.54000091552734</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>23.6534538269043</v>
+        <v>23.65344619750977</v>
       </c>
       <c r="C118" t="n">
         <v>30.13999938964844</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>26.57285308837891</v>
+        <v>26.57285118103027</v>
       </c>
       <c r="C119" t="n">
         <v>33.86000061035156</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>27.47922897338867</v>
+        <v>27.47922325134277</v>
       </c>
       <c r="C120" t="n">
         <v>34.77000045776367</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>27.2263240814209</v>
+        <v>27.22632789611816</v>
       </c>
       <c r="C121" t="n">
         <v>34.45000076293945</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>24.51554489135742</v>
+        <v>24.51554679870605</v>
       </c>
       <c r="C122" t="n">
         <v>31.02000045776367</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>23.59122848510742</v>
+        <v>23.59122085571289</v>
       </c>
       <c r="C123" t="n">
         <v>29.59000015258789</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>24.14134216308594</v>
+        <v>24.1413459777832</v>
       </c>
       <c r="C125" t="n">
         <v>30.28000068664551</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>26.37635040283203</v>
+        <v>26.37634658813477</v>
       </c>
       <c r="C127" t="n">
         <v>32.79999923706055</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>28.03290367126465</v>
+        <v>28.03291511535645</v>
       </c>
       <c r="C128" t="n">
         <v>34.86000061035156</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.0799617767334</v>
+        <v>29.07996559143066</v>
       </c>
       <c r="C129" t="n">
         <v>35.88999938964844</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.5870361328125</v>
+        <v>30.58703422546387</v>
       </c>
       <c r="C130" t="n">
         <v>37.75</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>28.25350570678711</v>
+        <v>28.25351524353027</v>
       </c>
       <c r="C131" t="n">
         <v>34.86999893188477</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>28.32864379882812</v>
+        <v>28.32863235473633</v>
       </c>
       <c r="C132" t="n">
         <v>34.70000076293945</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>29.61037254333496</v>
+        <v>29.61036682128906</v>
       </c>
       <c r="C133" t="n">
         <v>36.27000045776367</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.05938339233398</v>
+        <v>30.05937576293945</v>
       </c>
       <c r="C134" t="n">
         <v>36.81999969482422</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>29.76420211791992</v>
+        <v>29.76419639587402</v>
       </c>
       <c r="C135" t="n">
         <v>36.20000076293945</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.72308540344238</v>
+        <v>29.72308349609375</v>
       </c>
       <c r="C137" t="n">
         <v>36.15000152587891</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>29.91107559204102</v>
+        <v>29.91107749938965</v>
       </c>
       <c r="C138" t="n">
         <v>36.11000061035156</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>31.77967643737793</v>
+        <v>31.77967071533203</v>
       </c>
       <c r="C142" t="n">
         <v>38.08000183105469</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>37.96369934082031</v>
+        <v>37.96369171142578</v>
       </c>
       <c r="C143" t="n">
         <v>45.4900016784668</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>37.64301300048828</v>
+        <v>37.64298629760742</v>
       </c>
       <c r="C144" t="n">
         <v>44.84000015258789</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>40.41333770751953</v>
+        <v>40.41333389282227</v>
       </c>
       <c r="C146" t="n">
         <v>48.13999938964844</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>41.65947723388672</v>
+        <v>41.65948486328125</v>
       </c>
       <c r="C147" t="n">
         <v>49.29000091552734</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>44.01757049560547</v>
+        <v>44.0175666809082</v>
       </c>
       <c r="C148" t="n">
         <v>52.08000183105469</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>43.6287727355957</v>
+        <v>43.62878799438477</v>
       </c>
       <c r="C149" t="n">
         <v>51.61999893188477</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>42.25695037841797</v>
+        <v>42.25693511962891</v>
       </c>
       <c r="C151" t="n">
         <v>49.70999908447266</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>40.88832855224609</v>
+        <v>40.88833236694336</v>
       </c>
       <c r="C152" t="n">
         <v>48.09999847412109</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>41.41922378540039</v>
+        <v>41.41921615600586</v>
       </c>
       <c r="C153" t="n">
         <v>48.43000030517578</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>40.44426345825195</v>
+        <v>40.44424819946289</v>
       </c>
       <c r="C154" t="n">
         <v>47.29000091552734</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>40.09360504150391</v>
+        <v>40.09359359741211</v>
       </c>
       <c r="C155" t="n">
         <v>46.88000106811523</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>40.55246353149414</v>
+        <v>40.55247497558594</v>
       </c>
       <c r="C158" t="n">
         <v>47.11999893188477</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>45.86740493774414</v>
+        <v>45.86740112304688</v>
       </c>
       <c r="C159" t="n">
         <v>52.95999908447266</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>46.50830078125</v>
+        <v>46.50830459594727</v>
       </c>
       <c r="C160" t="n">
         <v>53.70000076293945</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>44.20454025268555</v>
+        <v>44.20454788208008</v>
       </c>
       <c r="C161" t="n">
         <v>51.04000091552734</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>38.37559509277344</v>
+        <v>38.3755989074707</v>
       </c>
       <c r="C162" t="n">
         <v>44.04000091552734</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>41.71297454833984</v>
+        <v>41.71298599243164</v>
       </c>
       <c r="C163" t="n">
         <v>47.86999893188477</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>44.04828643798828</v>
+        <v>44.04827880859375</v>
       </c>
       <c r="C164" t="n">
         <v>50.54999923706055</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>41.59106826782227</v>
+        <v>41.59107208251953</v>
       </c>
       <c r="C165" t="n">
         <v>47.40999984741211</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>45.20540618896484</v>
+        <v>45.20540237426758</v>
       </c>
       <c r="C166" t="n">
         <v>51.52999877929688</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>52.79319381713867</v>
+        <v>52.79319763183594</v>
       </c>
       <c r="C169" t="n">
         <v>59.84999847412109</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>47.97389602661133</v>
+        <v>47.97390365600586</v>
       </c>
       <c r="C172" t="n">
         <v>54.11999893188477</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>53.16842269897461</v>
+        <v>53.16841888427734</v>
       </c>
       <c r="C173" t="n">
         <v>59.97999954223633</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>56.0985221862793</v>
+        <v>56.0985107421875</v>
       </c>
       <c r="C174" t="n">
         <v>62.93000030517578</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>53.33504486083984</v>
+        <v>53.33503723144531</v>
       </c>
       <c r="C175" t="n">
         <v>59.83000183105469</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>42.548583984375</v>
+        <v>42.54857635498047</v>
       </c>
       <c r="C176" t="n">
         <v>47.72999954223633</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>39.74118423461914</v>
+        <v>39.74118041992188</v>
       </c>
       <c r="C179" t="n">
         <v>44.27999877929688</v>
@@ -5158,7 +5158,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>43.70962524414062</v>
+        <v>43.70962142944336</v>
       </c>
       <c r="C180" t="n">
         <v>48.34999847412109</v>
@@ -5187,7 +5187,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>45.03854370117188</v>
+        <v>45.03853988647461</v>
       </c>
       <c r="C181" t="n">
         <v>49.81999969482422</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>50.18244552612305</v>
+        <v>50.18244171142578</v>
       </c>
       <c r="C182" t="n">
         <v>55.5099983215332</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>58.20881652832031</v>
+        <v>58.20880889892578</v>
       </c>
       <c r="C184" t="n">
         <v>64</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>52.32426452636719</v>
+        <v>52.32426834106445</v>
       </c>
       <c r="C185" t="n">
         <v>57.52999877929688</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>52.27134323120117</v>
+        <v>52.27133941650391</v>
       </c>
       <c r="C186" t="n">
         <v>57.11999893188477</v>
@@ -5390,7 +5390,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>49.15994644165039</v>
+        <v>49.15994262695312</v>
       </c>
       <c r="C188" t="n">
         <v>53.72000122070312</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>49.79256439208984</v>
+        <v>49.79256820678711</v>
       </c>
       <c r="C189" t="n">
         <v>54.06000137329102</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>49.07414245605469</v>
+        <v>49.07413864135742</v>
       </c>
       <c r="C190" t="n">
         <v>53.27999877929688</v>
@@ -5477,7 +5477,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>45.13200759887695</v>
+        <v>45.13199234008789</v>
       </c>
       <c r="C191" t="n">
         <v>49</v>
@@ -5564,7 +5564,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>45.27890777587891</v>
+        <v>45.27891159057617</v>
       </c>
       <c r="C194" t="n">
         <v>48.81999969482422</v>
@@ -5622,7 +5622,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>46.31538009643555</v>
+        <v>46.31537628173828</v>
       </c>
       <c r="C196" t="n">
         <v>49.56000137329102</v>
@@ -5680,7 +5680,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>41.84003067016602</v>
+        <v>41.84002304077148</v>
       </c>
       <c r="C198" t="n">
         <v>44.41999816894531</v>
@@ -5709,7 +5709,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>35.23717498779297</v>
+        <v>35.23717880249023</v>
       </c>
       <c r="C199" t="n">
         <v>37.40999984741211</v>
@@ -5767,7 +5767,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>30.36957550048828</v>
+        <v>30.36957359313965</v>
       </c>
       <c r="C201" t="n">
         <v>31.92000007629395</v>
@@ -5796,7 +5796,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>24.51829147338867</v>
+        <v>24.5182933807373</v>
       </c>
       <c r="C202" t="n">
         <v>25.77000045776367</v>
@@ -5970,7 +5970,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>31.88681221008301</v>
+        <v>31.88681030273438</v>
       </c>
       <c r="C208" t="n">
         <v>32.66999816894531</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>30.31540870666504</v>
+        <v>30.31541061401367</v>
       </c>
       <c r="C209" t="n">
         <v>31.05999946594238</v>
@@ -6026,7 +6026,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>30.81196594238281</v>
+        <v>30.81196212768555</v>
       </c>
       <c r="C210" t="n">
         <v>31.44000053405762</v>
@@ -6080,7 +6080,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>35.05547332763672</v>
+        <v>35.05546569824219</v>
       </c>
       <c r="C212" t="n">
         <v>35.77000045776367</v>
@@ -6107,7 +6107,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>34.56195068359375</v>
+        <v>34.56194686889648</v>
       </c>
       <c r="C213" t="n">
         <v>35.13999938964844</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>35.89957427978516</v>
+        <v>35.89958190917969</v>
       </c>
       <c r="C215" t="n">
         <v>36.5</v>
@@ -6188,7 +6188,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>44.10924911499023</v>
+        <v>44.1092529296875</v>
       </c>
       <c r="C216" t="n">
         <v>44.70000076293945</v>
